--- a/outputs/49036.xlsx
+++ b/outputs/49036.xlsx
@@ -120,16 +120,15 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="0%&quot; WIN RATE&quot;"/>
-    <numFmt numFmtId="169" formatCode="h:mm"/>
-    <numFmt numFmtId="170" formatCode="0%"/>
-    <numFmt numFmtId="171" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="172" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="h:mm"/>
+    <numFmt numFmtId="169" formatCode="0%"/>
+    <numFmt numFmtId="170" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="171" formatCode="#,##0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -388,200 +387,204 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="13" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="170" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="15" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="170" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="18" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -961,126 +964,126 @@
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="25.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="22.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="21.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="25.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="22.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="21.66"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3"/>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="3"/>
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="4"/>
     </row>
     <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="5"/>
-      <c r="E2" s="3"/>
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="5"/>
+      <c r="D2" s="6"/>
+      <c r="E2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6"/>
-      <c r="B3" s="7"/>
-      <c r="C3" s="8" t="s">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="D3" s="9"/>
-      <c r="E3" s="10"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="11"/>
     </row>
     <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="8"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="10"/>
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="12"/>
+      <c r="E4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12"/>
-      <c r="B5" s="13" t="str">
+      <c r="A5" s="13"/>
+      <c r="B5" s="14" t="str">
         <f aca="false">SUMPRODUCT(COUNTIF(Trades!C:C,{"LONG","SHORT"}))&amp;" TRADES"</f>
         <v>3 TRADES</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="16" t="n">
         <v>100000</v>
       </c>
-      <c r="E5" s="16"/>
+      <c r="E5" s="17"/>
     </row>
     <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12"/>
-      <c r="B6" s="17" t="str">
+      <c r="A6" s="13"/>
+      <c r="B6" s="18" t="str">
         <f aca="false">SUMPRODUCT(COUNTIFS(Trades!N:N,"NO",Trades!C:C,{"LONG","SHORT"}))&amp;" GOOD TRADES"</f>
         <v>2 GOOD TRADES</v>
       </c>
-      <c r="C6" s="18" t="s">
+      <c r="C6" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="19" t="n">
+      <c r="D6" s="20" t="n">
         <f aca="false">SUM(Table1[P&amp;L %])</f>
         <v>-0.319227550767853</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="21"/>
     </row>
     <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12"/>
-      <c r="B7" s="17" t="str">
+      <c r="A7" s="13"/>
+      <c r="B7" s="18" t="str">
         <f aca="false">SUMPRODUCT(COUNTIFS(Trades!N:N,"YES",Trades!C:C,{"LONG","SHORT"}))&amp;" BAD TRADES"</f>
         <v>1 BAD TRADES</v>
       </c>
-      <c r="C7" s="18" t="s">
+      <c r="C7" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="22" t="n">
         <f aca="false">SUM(Table1[P&amp;L $])</f>
         <v>-20511</v>
       </c>
-      <c r="E7" s="22"/>
+      <c r="E7" s="23"/>
     </row>
     <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12"/>
-      <c r="B8" s="23" t="n">
-        <f aca="false">VALUE(LEFT(B6,FIND(" ",B6)-1))/VALUE(LEFT(B5,FIND(" ",B5)-1))</f>
-        <v>0.666666666666667</v>
-      </c>
-      <c r="C8" s="24" t="s">
+      <c r="A8" s="13"/>
+      <c r="B8" s="24" t="str">
+        <f aca="false">TEXT(VALUE(LEFT(B6,FIND(" ",B6)-1))/VALUE(LEFT(B5,FIND(" ",B5)-1)),"0%")&amp;" WIN RATE"</f>
+        <v>67% WIN RATE</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="22" t="n">
         <f aca="false">SUM(Table1[Commission])</f>
         <v>242</v>
       </c>
-      <c r="E8" s="22"/>
+      <c r="E8" s="23"/>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="26" t="s">
+      <c r="A9" s="13"/>
+      <c r="B9" s="26"/>
+      <c r="C9" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="27" t="n">
+      <c r="D9" s="28" t="n">
         <f aca="false">SUM(D5,D7)-D8</f>
         <v>79247</v>
       </c>
-      <c r="E9" s="28"/>
+      <c r="E9" s="29"/>
     </row>
     <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="3"/>
+      <c r="A10" s="4"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="6"/>
+      <c r="E10" s="4"/>
     </row>
     <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="3"/>
+      <c r="A11" s="4"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1113,563 +1116,563 @@
   <dimension ref="A1:N16"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="29" width="21.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="30" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="31" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="32" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="30" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="33" width="12.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="34" width="12.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="30" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="30" width="21.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="2" style="31" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="32" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="5" style="33" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="31" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="34" width="12.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="10" style="35" width="12.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="15" style="31" width="9.11"/>
   </cols>
   <sheetData>
-    <row r="1" s="36" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="35" t="s">
+    <row r="1" s="37" customFormat="true" ht="24.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="36" t="s">
+      <c r="B1" s="37" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="36" t="s">
+      <c r="C1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="37" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="37" t="s">
         <v>14</v>
       </c>
-      <c r="J1" s="37" t="s">
+      <c r="J1" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="37" t="s">
+      <c r="K1" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="L1" s="37" t="s">
+      <c r="L1" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="M1" s="37" t="s">
+      <c r="M1" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="N1" s="37" t="s">
+      <c r="N1" s="38" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="38" t="n">
+      <c r="A2" s="39" t="n">
         <v>44531</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="30" t="s">
+      <c r="C2" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="32" t="n">
+      <c r="D2" s="33" t="n">
         <v>7.13</v>
       </c>
-      <c r="E2" s="32" t="n">
+      <c r="E2" s="33" t="n">
         <v>7.64</v>
       </c>
-      <c r="F2" s="32" t="n">
+      <c r="F2" s="33" t="n">
         <v>6.82</v>
       </c>
-      <c r="G2" s="39" t="n">
+      <c r="G2" s="40" t="n">
         <v>7900</v>
       </c>
-      <c r="H2" s="32" t="n">
+      <c r="H2" s="33" t="n">
         <f aca="false">IF(OR(E2="",D2="",G2="",C2="")=TRUE(),"",IF(C2="LONG",(E2-D2)*G2,IF(C2="SHORT",(D2-E2)*G2)))</f>
         <v>4029</v>
       </c>
-      <c r="I2" s="40" t="n">
+      <c r="I2" s="41" t="n">
         <f aca="false">IF(OR(E2="",D2="",C2="")=TRUE(),"",IF(C2="LONG",(E2-D2)/D2,IF(C2="SHORT",(D2-E2)/D2)))</f>
         <v>0.0715287517531557</v>
       </c>
-      <c r="J2" s="41" t="n">
+      <c r="J2" s="42" t="n">
         <f aca="false">IF(OR(D2="",G2=""),"",(D2*G2))</f>
         <v>56327</v>
       </c>
-      <c r="K2" s="42" t="n">
+      <c r="K2" s="43" t="n">
         <f aca="false">IF(OR(F2="",D2="",C2="")=TRUE(),"",IF(C2="LONG",(D2-F2)/D2,IF(C2="SHORT",(F2-D2)/D2)))</f>
         <v>0.0434782608695652</v>
       </c>
-      <c r="L2" s="41" t="n">
+      <c r="L2" s="42" t="n">
         <f aca="false">IF(OR(J2="",K2=""),"",(J2*K2))</f>
         <v>2449</v>
       </c>
-      <c r="M2" s="41" t="n">
+      <c r="M2" s="42" t="n">
         <f aca="false">IF(G2,G2*0.005,"")</f>
         <v>39.5</v>
       </c>
-      <c r="N2" s="41" t="s">
+      <c r="N2" s="42" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="38" t="n">
+      <c r="A3" s="39" t="n">
         <v>44531</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="30" t="s">
+      <c r="C3" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="32" t="n">
+      <c r="D3" s="33" t="n">
         <v>4.76</v>
       </c>
-      <c r="E3" s="32" t="n">
+      <c r="E3" s="33" t="n">
         <v>5.28</v>
       </c>
-      <c r="F3" s="32" t="n">
+      <c r="F3" s="33" t="n">
         <v>4.49</v>
       </c>
-      <c r="G3" s="39" t="n">
+      <c r="G3" s="40" t="n">
         <v>10500</v>
       </c>
-      <c r="H3" s="32" t="n">
+      <c r="H3" s="33" t="n">
         <f aca="false">IF(OR(E3="",D3="",G3="",C3="")=TRUE(),"",IF(C3="LONG",(E3-D3)*G3,IF(C3="SHORT",(D3-E3)*G3)))</f>
         <v>5460.00000000001</v>
       </c>
-      <c r="I3" s="40" t="n">
+      <c r="I3" s="41" t="n">
         <f aca="false">IF(OR(E3="",D3="",C3="")=TRUE(),"",IF(C3="LONG",(E3-D3)/D3,IF(C3="SHORT",(D3-E3)/D3)))</f>
         <v>0.109243697478992</v>
       </c>
-      <c r="J3" s="41" t="n">
+      <c r="J3" s="42" t="n">
         <f aca="false">IF(OR(D3="",G3=""),"",(D3*G3))</f>
         <v>49980</v>
       </c>
-      <c r="K3" s="42" t="n">
+      <c r="K3" s="43" t="n">
         <f aca="false">IF(OR(F3="",D3="",C3="")=TRUE(),"",IF(C3="LONG",(D3-F3)/D3,IF(C3="SHORT",(F3-D3)/D3)))</f>
         <v>0.0567226890756302</v>
       </c>
-      <c r="L3" s="41" t="n">
+      <c r="L3" s="42" t="n">
         <f aca="false">IF(OR(J3="",K3=""),"",(J3*K3))</f>
         <v>2835</v>
       </c>
-      <c r="M3" s="32" t="n">
+      <c r="M3" s="33" t="n">
         <f aca="false">IF(G3,G3*0.005,"")</f>
         <v>52.5</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="42" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="38" t="n">
+      <c r="A4" s="39" t="n">
         <v>44531</v>
       </c>
-      <c r="B4" s="30" t="s">
+      <c r="B4" s="31" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="30" t="s">
+      <c r="C4" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="32" t="n">
+      <c r="D4" s="33" t="n">
         <v>2</v>
       </c>
-      <c r="E4" s="32" t="n">
+      <c r="E4" s="33" t="n">
         <v>1</v>
       </c>
-      <c r="F4" s="32" t="n">
+      <c r="F4" s="33" t="n">
         <v>1.1</v>
       </c>
-      <c r="G4" s="39" t="n">
+      <c r="G4" s="40" t="n">
         <v>30000</v>
       </c>
-      <c r="H4" s="32" t="n">
+      <c r="H4" s="33" t="n">
         <f aca="false">IF(OR(E4="",D4="",G4="",C4="")=TRUE(),"",IF(C4="LONG",(E4-D4)*G4,IF(C4="SHORT",(D4-E4)*G4)))</f>
         <v>-30000</v>
       </c>
-      <c r="I4" s="40" t="n">
+      <c r="I4" s="41" t="n">
         <f aca="false">IF(OR(E4="",D4="",C4="")=TRUE(),"",IF(C4="LONG",(E4-D4)/D4,IF(C4="SHORT",(D4-E4)/D4)))</f>
         <v>-0.5</v>
       </c>
-      <c r="J4" s="41" t="n">
+      <c r="J4" s="42" t="n">
         <f aca="false">IF(OR(D4="",G4=""),"",(D4*G4))</f>
         <v>60000</v>
       </c>
-      <c r="K4" s="42" t="n">
+      <c r="K4" s="43" t="n">
         <f aca="false">IF(OR(F4="",D4="",C4="")=TRUE(),"",IF(C4="LONG",(D4-F4)/D4,IF(C4="SHORT",(F4-D4)/D4)))</f>
         <v>0.45</v>
       </c>
-      <c r="L4" s="41" t="n">
+      <c r="L4" s="42" t="n">
         <f aca="false">IF(OR(J4="",K4=""),"",(J4*K4))</f>
         <v>27000</v>
       </c>
-      <c r="M4" s="32" t="n">
+      <c r="M4" s="33" t="n">
         <f aca="false">IF(G4,G4*0.005,"")</f>
         <v>150</v>
       </c>
-      <c r="N4" s="41" t="s">
+      <c r="N4" s="42" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="36"/>
-      <c r="D5" s="32"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="32" t="str">
+      <c r="A5" s="37"/>
+      <c r="D5" s="33"/>
+      <c r="G5" s="40"/>
+      <c r="H5" s="33" t="str">
         <f aca="false">IF(OR(E5="",D5="",G5="",C5="")=TRUE(),"",IF(C5="LONG",(E5-D5)*G5,IF(C5="SHORT",(D5-E5)*G5)))</f>
         <v/>
       </c>
-      <c r="I5" s="40" t="str">
+      <c r="I5" s="41" t="str">
         <f aca="false">IF(OR(E5="",D5="",C5="")=TRUE(),"",IF(C5="LONG",(E5-D5)/D5,IF(C5="SHORT",(D5-E5)/D5)))</f>
         <v/>
       </c>
-      <c r="J5" s="41" t="str">
+      <c r="J5" s="42" t="str">
         <f aca="false">IF(OR(D5="",G5=""),"",(D5*G5))</f>
         <v/>
       </c>
-      <c r="K5" s="42" t="str">
+      <c r="K5" s="43" t="str">
         <f aca="false">IF(OR(F5="",D5="",C5="")=TRUE(),"",IF(C5="LONG",(D5-F5)/D5,IF(C5="SHORT",(F5-D5)/D5)))</f>
         <v/>
       </c>
-      <c r="L5" s="41" t="str">
+      <c r="L5" s="42" t="str">
         <f aca="false">IF(OR(J5="",K5=""),"",(J5*K5))</f>
         <v/>
       </c>
-      <c r="M5" s="32" t="str">
+      <c r="M5" s="33" t="str">
         <f aca="false">IF(G5,G5*0.005,"")</f>
         <v/>
       </c>
-      <c r="N5" s="41"/>
+      <c r="N5" s="42"/>
     </row>
     <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="36"/>
-      <c r="D6" s="32"/>
-      <c r="G6" s="39"/>
-      <c r="H6" s="32" t="str">
+      <c r="A6" s="37"/>
+      <c r="D6" s="33"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="33" t="str">
         <f aca="false">IF(OR(E6="",D6="",G6="",C6="")=TRUE(),"",IF(C6="LONG",(E6-D6)*G6,IF(C6="SHORT",(D6-E6)*G6)))</f>
         <v/>
       </c>
-      <c r="I6" s="40" t="str">
+      <c r="I6" s="41" t="str">
         <f aca="false">IF(OR(E6="",D6="",C6="")=TRUE(),"",IF(C6="LONG",(E6-D6)/D6,IF(C6="SHORT",(D6-E6)/D6)))</f>
         <v/>
       </c>
-      <c r="J6" s="41" t="str">
+      <c r="J6" s="42" t="str">
         <f aca="false">IF(OR(D6="",G6=""),"",(D6*G6))</f>
         <v/>
       </c>
-      <c r="K6" s="42" t="str">
+      <c r="K6" s="43" t="str">
         <f aca="false">IF(OR(F6="",D6="",C6="")=TRUE(),"",IF(C6="LONG",(D6-F6)/D6,IF(C6="SHORT",(F6-D6)/D6)))</f>
         <v/>
       </c>
-      <c r="L6" s="41" t="str">
+      <c r="L6" s="42" t="str">
         <f aca="false">IF(OR(J6="",K6=""),"",(J6*K6))</f>
         <v/>
       </c>
-      <c r="M6" s="32" t="str">
+      <c r="M6" s="33" t="str">
         <f aca="false">IF(G6,G6*0.005,"")</f>
         <v/>
       </c>
-      <c r="N6" s="41"/>
+      <c r="N6" s="42"/>
     </row>
     <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="36"/>
-      <c r="D7" s="32"/>
-      <c r="G7" s="39"/>
-      <c r="H7" s="32" t="str">
+      <c r="A7" s="37"/>
+      <c r="D7" s="33"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="33" t="str">
         <f aca="false">IF(OR(E7="",D7="",G7="",C7="")=TRUE(),"",IF(C7="LONG",(E7-D7)*G7,IF(C7="SHORT",(D7-E7)*G7)))</f>
         <v/>
       </c>
-      <c r="I7" s="40" t="str">
+      <c r="I7" s="41" t="str">
         <f aca="false">IF(OR(E7="",D7="",C7="")=TRUE(),"",IF(C7="LONG",(E7-D7)/D7,IF(C7="SHORT",(D7-E7)/D7)))</f>
         <v/>
       </c>
-      <c r="J7" s="41" t="str">
+      <c r="J7" s="42" t="str">
         <f aca="false">IF(OR(D7="",G7=""),"",(D7*G7))</f>
         <v/>
       </c>
-      <c r="K7" s="42" t="str">
+      <c r="K7" s="43" t="str">
         <f aca="false">IF(OR(F7="",D7="",C7="")=TRUE(),"",IF(C7="LONG",(D7-F7)/D7,IF(C7="SHORT",(F7-D7)/D7)))</f>
         <v/>
       </c>
-      <c r="L7" s="41" t="str">
+      <c r="L7" s="42" t="str">
         <f aca="false">IF(OR(J7="",K7=""),"",(J7*K7))</f>
         <v/>
       </c>
-      <c r="M7" s="32" t="str">
+      <c r="M7" s="33" t="str">
         <f aca="false">IF(G7,G7*0.005,"")</f>
         <v/>
       </c>
-      <c r="N7" s="41"/>
+      <c r="N7" s="42"/>
     </row>
     <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="36"/>
-      <c r="D8" s="32"/>
-      <c r="G8" s="39"/>
-      <c r="H8" s="32" t="str">
+      <c r="A8" s="37"/>
+      <c r="D8" s="33"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="33" t="str">
         <f aca="false">IF(OR(E8="",D8="",G8="",C8="")=TRUE(),"",IF(C8="LONG",(E8-D8)*G8,IF(C8="SHORT",(D8-E8)*G8)))</f>
         <v/>
       </c>
-      <c r="I8" s="40" t="str">
+      <c r="I8" s="41" t="str">
         <f aca="false">IF(OR(E8="",D8="",C8="")=TRUE(),"",IF(C8="LONG",(E8-D8)/D8,IF(C8="SHORT",(D8-E8)/D8)))</f>
         <v/>
       </c>
-      <c r="J8" s="41" t="str">
+      <c r="J8" s="42" t="str">
         <f aca="false">IF(OR(D8="",G8=""),"",(D8*G8))</f>
         <v/>
       </c>
-      <c r="K8" s="42" t="str">
+      <c r="K8" s="43" t="str">
         <f aca="false">IF(OR(F8="",D8="",C8="")=TRUE(),"",IF(C8="LONG",(D8-F8)/D8,IF(C8="SHORT",(F8-D8)/D8)))</f>
         <v/>
       </c>
-      <c r="L8" s="41" t="str">
+      <c r="L8" s="42" t="str">
         <f aca="false">IF(OR(J8="",K8=""),"",(J8*K8))</f>
         <v/>
       </c>
-      <c r="M8" s="32" t="str">
+      <c r="M8" s="33" t="str">
         <f aca="false">IF(G8,G8*0.005,"")</f>
         <v/>
       </c>
-      <c r="N8" s="41"/>
+      <c r="N8" s="42"/>
     </row>
     <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="36"/>
-      <c r="D9" s="32"/>
-      <c r="G9" s="39"/>
-      <c r="H9" s="32" t="str">
+      <c r="A9" s="37"/>
+      <c r="D9" s="33"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="33" t="str">
         <f aca="false">IF(OR(E9="",D9="",G9="",C9="")=TRUE(),"",IF(C9="LONG",(E9-D9)*G9,IF(C9="SHORT",(D9-E9)*G9)))</f>
         <v/>
       </c>
-      <c r="I9" s="40" t="str">
+      <c r="I9" s="41" t="str">
         <f aca="false">IF(OR(E9="",D9="",C9="")=TRUE(),"",IF(C9="LONG",(E9-D9)/D9,IF(C9="SHORT",(D9-E9)/D9)))</f>
         <v/>
       </c>
-      <c r="J9" s="41" t="str">
+      <c r="J9" s="42" t="str">
         <f aca="false">IF(OR(D9="",G9=""),"",(D9*G9))</f>
         <v/>
       </c>
-      <c r="K9" s="42" t="str">
+      <c r="K9" s="43" t="str">
         <f aca="false">IF(OR(F9="",D9="",C9="")=TRUE(),"",IF(C9="LONG",(D9-F9)/D9,IF(C9="SHORT",(F9-D9)/D9)))</f>
         <v/>
       </c>
-      <c r="L9" s="41" t="str">
+      <c r="L9" s="42" t="str">
         <f aca="false">IF(OR(J9="",K9=""),"",(J9*K9))</f>
         <v/>
       </c>
-      <c r="M9" s="32" t="str">
+      <c r="M9" s="33" t="str">
         <f aca="false">IF(G9,G9*0.005,"")</f>
         <v/>
       </c>
-      <c r="N9" s="41"/>
+      <c r="N9" s="42"/>
     </row>
     <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="36"/>
-      <c r="D10" s="32"/>
-      <c r="G10" s="39"/>
-      <c r="H10" s="32" t="str">
+      <c r="A10" s="37"/>
+      <c r="D10" s="33"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="33" t="str">
         <f aca="false">IF(OR(E10="",D10="",G10="",C10="")=TRUE(),"",IF(C10="LONG",(E10-D10)*G10,IF(C10="SHORT",(D10-E10)*G10)))</f>
         <v/>
       </c>
-      <c r="I10" s="40" t="str">
+      <c r="I10" s="41" t="str">
         <f aca="false">IF(OR(E10="",D10="",C10="")=TRUE(),"",IF(C10="LONG",(E10-D10)/D10,IF(C10="SHORT",(D10-E10)/D10)))</f>
         <v/>
       </c>
-      <c r="J10" s="41" t="str">
+      <c r="J10" s="42" t="str">
         <f aca="false">IF(OR(D10="",G10=""),"",(D10*G10))</f>
         <v/>
       </c>
-      <c r="K10" s="42" t="str">
+      <c r="K10" s="43" t="str">
         <f aca="false">IF(OR(F10="",D10="",C10="")=TRUE(),"",IF(C10="LONG",(D10-F10)/D10,IF(C10="SHORT",(F10-D10)/D10)))</f>
         <v/>
       </c>
-      <c r="L10" s="41" t="str">
+      <c r="L10" s="42" t="str">
         <f aca="false">IF(OR(J10="",K10=""),"",(J10*K10))</f>
         <v/>
       </c>
-      <c r="M10" s="32" t="str">
+      <c r="M10" s="33" t="str">
         <f aca="false">IF(G10,G10*0.005,"")</f>
         <v/>
       </c>
-      <c r="N10" s="41"/>
+      <c r="N10" s="42"/>
     </row>
     <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="36"/>
-      <c r="D11" s="32"/>
-      <c r="G11" s="39"/>
-      <c r="H11" s="32" t="str">
+      <c r="A11" s="37"/>
+      <c r="D11" s="33"/>
+      <c r="G11" s="40"/>
+      <c r="H11" s="33" t="str">
         <f aca="false">IF(OR(E11="",D11="",G11="",C11="")=TRUE(),"",IF(C11="LONG",(E11-D11)*G11,IF(C11="SHORT",(D11-E11)*G11)))</f>
         <v/>
       </c>
-      <c r="I11" s="40" t="str">
+      <c r="I11" s="41" t="str">
         <f aca="false">IF(OR(E11="",D11="",C11="")=TRUE(),"",IF(C11="LONG",(E11-D11)/D11,IF(C11="SHORT",(D11-E11)/D11)))</f>
         <v/>
       </c>
-      <c r="J11" s="41" t="str">
+      <c r="J11" s="42" t="str">
         <f aca="false">IF(OR(D11="",G11=""),"",(D11*G11))</f>
         <v/>
       </c>
-      <c r="K11" s="42" t="str">
+      <c r="K11" s="43" t="str">
         <f aca="false">IF(OR(F11="",D11="",C11="")=TRUE(),"",IF(C11="LONG",(D11-F11)/D11,IF(C11="SHORT",(F11-D11)/D11)))</f>
         <v/>
       </c>
-      <c r="L11" s="41" t="str">
+      <c r="L11" s="42" t="str">
         <f aca="false">IF(OR(J11="",K11=""),"",(J11*K11))</f>
         <v/>
       </c>
-      <c r="M11" s="32" t="str">
+      <c r="M11" s="33" t="str">
         <f aca="false">IF(G11,G11*0.005,"")</f>
         <v/>
       </c>
-      <c r="N11" s="41"/>
+      <c r="N11" s="42"/>
     </row>
     <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="36"/>
-      <c r="D12" s="32"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="32" t="str">
+      <c r="A12" s="37"/>
+      <c r="D12" s="33"/>
+      <c r="G12" s="40"/>
+      <c r="H12" s="33" t="str">
         <f aca="false">IF(OR(E12="",D12="",G12="",C12="")=TRUE(),"",IF(C12="LONG",(E12-D12)*G12,IF(C12="SHORT",(D12-E12)*G12)))</f>
         <v/>
       </c>
-      <c r="I12" s="40" t="str">
+      <c r="I12" s="41" t="str">
         <f aca="false">IF(OR(E12="",D12="",C12="")=TRUE(),"",IF(C12="LONG",(E12-D12)/D12,IF(C12="SHORT",(D12-E12)/D12)))</f>
         <v/>
       </c>
-      <c r="J12" s="41" t="str">
+      <c r="J12" s="42" t="str">
         <f aca="false">IF(OR(D12="",G12=""),"",(D12*G12))</f>
         <v/>
       </c>
-      <c r="K12" s="42" t="str">
+      <c r="K12" s="43" t="str">
         <f aca="false">IF(OR(F12="",D12="",C12="")=TRUE(),"",IF(C12="LONG",(D12-F12)/D12,IF(C12="SHORT",(F12-D12)/D12)))</f>
         <v/>
       </c>
-      <c r="L12" s="41" t="str">
+      <c r="L12" s="42" t="str">
         <f aca="false">IF(OR(J12="",K12=""),"",(J12*K12))</f>
         <v/>
       </c>
-      <c r="M12" s="32" t="str">
+      <c r="M12" s="33" t="str">
         <f aca="false">IF(G12,G12*0.005,"")</f>
         <v/>
       </c>
-      <c r="N12" s="41"/>
+      <c r="N12" s="42"/>
     </row>
     <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="36"/>
-      <c r="D13" s="32"/>
-      <c r="G13" s="39"/>
-      <c r="H13" s="32" t="str">
+      <c r="A13" s="37"/>
+      <c r="D13" s="33"/>
+      <c r="G13" s="40"/>
+      <c r="H13" s="33" t="str">
         <f aca="false">IF(OR(E13="",D13="",G13="",C13="")=TRUE(),"",IF(C13="LONG",(E13-D13)*G13,IF(C13="SHORT",(D13-E13)*G13)))</f>
         <v/>
       </c>
-      <c r="I13" s="40" t="str">
+      <c r="I13" s="41" t="str">
         <f aca="false">IF(OR(E13="",D13="",C13="")=TRUE(),"",IF(C13="LONG",(E13-D13)/D13,IF(C13="SHORT",(D13-E13)/D13)))</f>
         <v/>
       </c>
-      <c r="J13" s="41" t="str">
+      <c r="J13" s="42" t="str">
         <f aca="false">IF(OR(D13="",G13=""),"",(D13*G13))</f>
         <v/>
       </c>
-      <c r="K13" s="42" t="str">
+      <c r="K13" s="43" t="str">
         <f aca="false">IF(OR(F13="",D13="",C13="")=TRUE(),"",IF(C13="LONG",(D13-F13)/D13,IF(C13="SHORT",(F13-D13)/D13)))</f>
         <v/>
       </c>
-      <c r="L13" s="41" t="str">
+      <c r="L13" s="42" t="str">
         <f aca="false">IF(OR(J13="",K13=""),"",(J13*K13))</f>
         <v/>
       </c>
-      <c r="M13" s="32" t="str">
+      <c r="M13" s="33" t="str">
         <f aca="false">IF(G13,G13*0.005,"")</f>
         <v/>
       </c>
-      <c r="N13" s="41"/>
+      <c r="N13" s="42"/>
     </row>
     <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="36"/>
-      <c r="D14" s="32"/>
-      <c r="G14" s="39"/>
-      <c r="H14" s="32" t="str">
+      <c r="A14" s="37"/>
+      <c r="D14" s="33"/>
+      <c r="G14" s="40"/>
+      <c r="H14" s="33" t="str">
         <f aca="false">IF(OR(E14="",D14="",G14="",C14="")=TRUE(),"",IF(C14="LONG",(E14-D14)*G14,IF(C14="SHORT",(D14-E14)*G14)))</f>
         <v/>
       </c>
-      <c r="I14" s="40" t="str">
+      <c r="I14" s="41" t="str">
         <f aca="false">IF(OR(E14="",D14="",C14="")=TRUE(),"",IF(C14="LONG",(E14-D14)/D14,IF(C14="SHORT",(D14-E14)/D14)))</f>
         <v/>
       </c>
-      <c r="J14" s="41" t="str">
+      <c r="J14" s="42" t="str">
         <f aca="false">IF(OR(D14="",G14=""),"",(D14*G14))</f>
         <v/>
       </c>
-      <c r="K14" s="42" t="str">
+      <c r="K14" s="43" t="str">
         <f aca="false">IF(OR(F14="",D14="",C14="")=TRUE(),"",IF(C14="LONG",(D14-F14)/D14,IF(C14="SHORT",(F14-D14)/D14)))</f>
         <v/>
       </c>
-      <c r="L14" s="41" t="str">
+      <c r="L14" s="42" t="str">
         <f aca="false">IF(OR(J14="",K14=""),"",(J14*K14))</f>
         <v/>
       </c>
-      <c r="M14" s="32" t="str">
+      <c r="M14" s="33" t="str">
         <f aca="false">IF(G14,G14*0.005,"")</f>
         <v/>
       </c>
-      <c r="N14" s="41"/>
+      <c r="N14" s="42"/>
     </row>
     <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="36"/>
-      <c r="D15" s="32"/>
-      <c r="G15" s="39"/>
-      <c r="H15" s="32" t="str">
+      <c r="A15" s="37"/>
+      <c r="D15" s="33"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="33" t="str">
         <f aca="false">IF(OR(E15="",D15="",G15="",C15="")=TRUE(),"",IF(C15="LONG",(E15-D15)*G15,IF(C15="SHORT",(D15-E15)*G15)))</f>
         <v/>
       </c>
-      <c r="I15" s="40" t="str">
+      <c r="I15" s="41" t="str">
         <f aca="false">IF(OR(E15="",D15="",C15="")=TRUE(),"",IF(C15="LONG",(E15-D15)/D15,IF(C15="SHORT",(D15-E15)/D15)))</f>
         <v/>
       </c>
-      <c r="J15" s="41" t="str">
+      <c r="J15" s="42" t="str">
         <f aca="false">IF(OR(D15="",G15=""),"",(D15*G15))</f>
         <v/>
       </c>
-      <c r="K15" s="42" t="str">
+      <c r="K15" s="43" t="str">
         <f aca="false">IF(OR(F15="",D15="",C15="")=TRUE(),"",IF(C15="LONG",(D15-F15)/D15,IF(C15="SHORT",(F15-D15)/D15)))</f>
         <v/>
       </c>
-      <c r="L15" s="41" t="str">
+      <c r="L15" s="42" t="str">
         <f aca="false">IF(OR(J15="",K15=""),"",(J15*K15))</f>
         <v/>
       </c>
-      <c r="M15" s="32" t="str">
+      <c r="M15" s="33" t="str">
         <f aca="false">IF(G15,G15*0.005,"")</f>
         <v/>
       </c>
-      <c r="N15" s="41"/>
+      <c r="N15" s="42"/>
     </row>
     <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
+      <c r="A16" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="32"/>
-      <c r="F16" s="44"/>
-      <c r="G16" s="45"/>
-      <c r="H16" s="44"/>
-      <c r="I16" s="46"/>
-      <c r="J16" s="44"/>
-      <c r="K16" s="47" t="str">
+      <c r="D16" s="33"/>
+      <c r="F16" s="45"/>
+      <c r="G16" s="46"/>
+      <c r="H16" s="45"/>
+      <c r="I16" s="47"/>
+      <c r="J16" s="45"/>
+      <c r="K16" s="48" t="str">
         <f aca="false">IF(OR(F16="",D16="",C16="")=TRUE(),"",IF(C16="LONG",(D16-F16)/D16,IF(C16="SHORT",(F16-D16)/D16)))</f>
         <v/>
       </c>
-      <c r="L16" s="41" t="str">
+      <c r="L16" s="42" t="str">
         <f aca="false">IF(OR(J16="",K16=""),"",(J16*K16))</f>
         <v/>
       </c>
-      <c r="M16" s="44" t="str">
+      <c r="M16" s="45" t="str">
         <f aca="false">IF(G16,G16*0.005,"")</f>
         <v/>
       </c>
-      <c r="N16" s="44"/>
+      <c r="N16" s="45"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="B11">
@@ -1725,27 +1728,27 @@
   <dimension ref="A1:A5"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="12" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="48" width="10.66"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="48" width="9.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="49" width="10.66"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="49" width="9.11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="48" t="s">
+      <c r="A1" s="49" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="48" t="s">
+      <c r="A4" s="49" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="48" t="s">
+      <c r="A5" s="49" t="s">
         <v>22</v>
       </c>
     </row>

--- a/outputs/49036.xlsx
+++ b/outputs/49036.xlsx
@@ -120,15 +120,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="\$#,##0"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="h:mm"/>
-    <numFmt numFmtId="169" formatCode="0%"/>
-    <numFmt numFmtId="170" formatCode="m/d/yyyy"/>
-    <numFmt numFmtId="171" formatCode="#,##0"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="h:mm"/>
+    <numFmt numFmtId="170" formatCode="0%"/>
+    <numFmt numFmtId="171" formatCode="m/d/yyyy"/>
+    <numFmt numFmtId="172" formatCode="#,##0"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -484,7 +485,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="168" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -516,7 +517,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="169" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -528,7 +529,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="170" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -544,11 +545,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="171" fontId="4" fillId="2" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -572,7 +573,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="172" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -970,21 +971,21 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="3" width="21.66"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="4"/>
       <c r="B1" s="4"/>
       <c r="C1" s="5"/>
       <c r="D1" s="6"/>
       <c r="E1" s="4"/>
     </row>
-    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="4"/>
       <c r="B2" s="4"/>
       <c r="C2" s="5"/>
       <c r="D2" s="6"/>
       <c r="E2" s="4"/>
     </row>
-    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="7"/>
       <c r="B3" s="8"/>
       <c r="C3" s="9" t="s">
@@ -993,14 +994,14 @@
       <c r="D3" s="10"/>
       <c r="E3" s="11"/>
     </row>
-    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="7"/>
       <c r="B4" s="8"/>
       <c r="C4" s="9"/>
       <c r="D4" s="12"/>
       <c r="E4" s="11"/>
     </row>
-    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13"/>
       <c r="B5" s="14" t="str">
         <f aca="false">SUMPRODUCT(COUNTIF(Trades!C:C,{"LONG","SHORT"}))&amp;" TRADES"</f>
@@ -1014,7 +1015,7 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13"/>
       <c r="B6" s="18" t="str">
         <f aca="false">SUMPRODUCT(COUNTIFS(Trades!N:N,"NO",Trades!C:C,{"LONG","SHORT"}))&amp;" GOOD TRADES"</f>
@@ -1029,7 +1030,7 @@
       </c>
       <c r="E6" s="21"/>
     </row>
-    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="13"/>
       <c r="B7" s="18" t="str">
         <f aca="false">SUMPRODUCT(COUNTIFS(Trades!N:N,"YES",Trades!C:C,{"LONG","SHORT"}))&amp;" BAD TRADES"</f>
@@ -1044,11 +1045,11 @@
       </c>
       <c r="E7" s="23"/>
     </row>
-    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13"/>
       <c r="B8" s="24" t="str">
-        <f aca="false">TEXT(VALUE(LEFT(B6,FIND(" ",B6)-1))/VALUE(LEFT(B5,FIND(" ",B5)-1)),"0%")&amp;" WIN RATE"</f>
-        <v>67% WIN RATE</v>
+        <f aca="false">VALUE(LEFT(B6,FIND(" ",B6)-1))/VALUE(LEFT(B5,FIND(" ",B5)-1))*100&amp;" WIN RATE"</f>
+        <v>66.6666666666667 WIN RATE</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>4</v>
@@ -1071,14 +1072,14 @@
       </c>
       <c r="E9" s="29"/>
     </row>
-    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="4"/>
       <c r="B10" s="4"/>
       <c r="C10" s="5"/>
       <c r="D10" s="6"/>
       <c r="E10" s="4"/>
     </row>
-    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="14.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="4"/>
       <c r="B11" s="4"/>
       <c r="C11" s="5"/>
@@ -1170,7 +1171,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="39" t="n">
         <v>44531</v>
       </c>
@@ -1220,7 +1221,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="39" t="n">
         <v>44531</v>
       </c>
@@ -1270,7 +1271,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="39" t="n">
         <v>44531</v>
       </c>
@@ -1320,7 +1321,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="37"/>
       <c r="D5" s="33"/>
       <c r="G5" s="40"/>
@@ -1350,7 +1351,7 @@
       </c>
       <c r="N5" s="42"/>
     </row>
-    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="37"/>
       <c r="D6" s="33"/>
       <c r="G6" s="40"/>
@@ -1380,7 +1381,7 @@
       </c>
       <c r="N6" s="42"/>
     </row>
-    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="37"/>
       <c r="D7" s="33"/>
       <c r="G7" s="40"/>
@@ -1410,7 +1411,7 @@
       </c>
       <c r="N7" s="42"/>
     </row>
-    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="37"/>
       <c r="D8" s="33"/>
       <c r="G8" s="40"/>
@@ -1440,7 +1441,7 @@
       </c>
       <c r="N8" s="42"/>
     </row>
-    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="37"/>
       <c r="D9" s="33"/>
       <c r="G9" s="40"/>
@@ -1470,7 +1471,7 @@
       </c>
       <c r="N9" s="42"/>
     </row>
-    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="37"/>
       <c r="D10" s="33"/>
       <c r="G10" s="40"/>
@@ -1500,7 +1501,7 @@
       </c>
       <c r="N10" s="42"/>
     </row>
-    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="37"/>
       <c r="D11" s="33"/>
       <c r="G11" s="40"/>
@@ -1530,7 +1531,7 @@
       </c>
       <c r="N11" s="42"/>
     </row>
-    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="37"/>
       <c r="D12" s="33"/>
       <c r="G12" s="40"/>
@@ -1560,7 +1561,7 @@
       </c>
       <c r="N12" s="42"/>
     </row>
-    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="37"/>
       <c r="D13" s="33"/>
       <c r="G13" s="40"/>
@@ -1590,7 +1591,7 @@
       </c>
       <c r="N13" s="42"/>
     </row>
-    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="37"/>
       <c r="D14" s="33"/>
       <c r="G14" s="40"/>
@@ -1620,7 +1621,7 @@
       </c>
       <c r="N14" s="42"/>
     </row>
-    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="37"/>
       <c r="D15" s="33"/>
       <c r="G15" s="40"/>
@@ -1650,7 +1651,7 @@
       </c>
       <c r="N15" s="42"/>
     </row>
-    <row r="16" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="16" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="44" t="s">
         <v>26</v>
       </c>
@@ -1732,22 +1733,22 @@
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="2" style="49" width="9.11"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="49" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="49" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="49" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="12" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="49" t="s">
         <v>22</v>
       </c>
